--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80668039-0B43-4968-AD5E-7CB71A2307A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="147">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -271,9 +285,6 @@
     <t>NameType2</t>
   </si>
   <si>
-    <t>AllowanceAmount</t>
-  </si>
-  <si>
     <t>Relationship1</t>
   </si>
   <si>
@@ -298,251 +309,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Queen Welch' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #59[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #60[22m
-[2m  -   waiting 500ms[22m
-</t>
+    <t>Test failed for 'Swift Bernadine' Employee: Errors and AlertsErrorsAlertNational IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\GKALE\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2025-03-17T06-08-45-952Z.png</t>
   </si>
   <si>
     <t>Failed</t>
@@ -614,7 +381,7 @@
     <t>Automation Comments here….</t>
   </si>
   <si>
-    <t xml:space="preserve">94 Retail Operatives </t>
+    <t>94 Retail Operatives </t>
   </si>
   <si>
     <t>16 Men’s Accessories</t>
@@ -639,7 +406,7 @@
     <t>Social Security</t>
   </si>
   <si>
-    <t>091602990</t>
+    <t>0786024787</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -699,66 +466,66 @@
     <t>Maiden Name</t>
   </si>
   <si>
-    <t>Queen</t>
-  </si>
-  <si>
-    <t>Welch</t>
+    <t>Pansy</t>
+  </si>
+  <si>
+    <t>Zieme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -770,13 +537,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -792,7 +559,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -802,69 +569,98 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -897,16 +693,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -927,7 +723,7 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -949,12 +745,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -962,10 +760,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1252,9 +1046,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CV2"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CU2"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="18.81640625" customWidth="1"/>
@@ -1268,6 +1062,7 @@
     <col min="32" max="32" width="18" customWidth="1"/>
     <col min="34" max="34" width="19.36328125" customWidth="1"/>
     <col min="35" max="35" width="20.453125" customWidth="1"/>
+    <col min="43" max="43" width="12.08984375" customWidth="1"/>
     <col min="49" max="49" width="24.26953125" customWidth="1"/>
     <col min="50" max="50" width="33.6328125" customWidth="1"/>
     <col min="52" max="52" width="38.453125" customWidth="1"/>
@@ -1277,11 +1072,15 @@
     <col min="59" max="59" width="55.7265625" customWidth="1"/>
     <col min="60" max="60" width="28.54296875" customWidth="1"/>
     <col min="61" max="61" width="29.36328125" customWidth="1"/>
-    <col min="100" max="100" width="31.54296875" customWidth="1"/>
-    <col min="101" max="101" width="21.1796875" customWidth="1"/>
+    <col min="65" max="65" width="34.36328125" customWidth="1"/>
+    <col min="66" max="66" width="26.08984375" customWidth="1"/>
+    <col min="78" max="78" width="21.6328125" customWidth="1"/>
+    <col min="79" max="79" width="23.26953125" customWidth="1"/>
+    <col min="99" max="99" width="54.81640625" customWidth="1"/>
+    <col min="100" max="100" width="21.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:99" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1357,7 @@
       <c r="CN1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CO1" s="12" t="s">
+      <c r="CO1" s="6" t="s">
         <v>85</v>
       </c>
       <c r="CP1" s="6" t="s">
@@ -1579,98 +1378,95 @@
       <c r="CU1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="CV1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:99" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" ht="87.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>97</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="J2" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="K2" s="19">
+        <f ca="1">TODAY()-31</f>
+        <v>45702</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="K2" s="19">
-        <f>TODAY()-31</f>
-        <v>45683</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="O2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="Q2" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="R2" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="S2" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="T2" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="T2" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="V2" s="25" t="s">
+      <c r="W2" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y2" s="19">
+        <f ca="1">K2</f>
+        <v>45702</v>
+      </c>
+      <c r="Z2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="X2" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y2" s="19">
-        <f>K2</f>
-        <v>45683</v>
-      </c>
-      <c r="Z2" s="18" t="s">
+      <c r="AA2" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="28" t="s">
+      <c r="AC2" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AC2" s="29" t="s">
+      <c r="AD2" s="30" t="s">
         <v>113</v>
-      </c>
-      <c r="AD2" s="30" t="s">
-        <v>114</v>
       </c>
       <c r="AE2" s="20">
         <v>846</v>
@@ -1682,88 +1478,88 @@
         <v>40</v>
       </c>
       <c r="AH2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI2" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AJ2" s="31">
+        <f ca="1">TODAY()+365</f>
+        <v>46098</v>
+      </c>
+      <c r="AK2" s="31">
+        <f ca="1">Y2+90</f>
+        <v>45792</v>
+      </c>
+      <c r="AL2" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="AJ2" s="31">
-        <f>TODAY()+365</f>
-        <v>46079</v>
-      </c>
-      <c r="AK2" s="31">
-        <f>Y2+90</f>
-        <v>45773</v>
-      </c>
-      <c r="AL2" s="18" t="s">
+      <c r="AM2" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="AM2" s="30" t="s">
+      <c r="AN2" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="AN2" s="29" t="s">
+      <c r="AO2" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AO2" s="18" t="s">
+      <c r="AP2" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="AP2" s="32" t="s">
+      <c r="AQ2" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AR2" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="AS2" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT2" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="AR2" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="AS2" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT2" s="18" t="s">
-        <v>123</v>
       </c>
       <c r="AU2" s="32" t="str">
         <f>AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW2" s="33">
+        <f ca="1">Y2-1</f>
+        <v>45701</v>
+      </c>
+      <c r="AX2" s="33">
+        <f ca="1">Y2-1</f>
+        <v>45701</v>
+      </c>
+      <c r="AY2" s="31">
+        <f ca="1">AJ2</f>
+        <v>46098</v>
+      </c>
+      <c r="AZ2" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA2" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="AW2" s="33">
-        <f>Y2-1</f>
-        <v>45682</v>
-      </c>
-      <c r="AX2" s="33">
-        <f>Y2-1</f>
-        <v>45682</v>
-      </c>
-      <c r="AY2" s="31">
-        <f>AJ2</f>
-        <v>46079</v>
-      </c>
-      <c r="AZ2" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA2" s="24" t="s">
+      <c r="BB2" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BB2" s="34" t="s">
+      <c r="BC2" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="BC2" s="25" t="s">
+      <c r="BD2" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="BD2" s="25" t="s">
+      <c r="BE2" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="BF2" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="BE2" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="BF2" s="24" t="s">
-        <v>129</v>
-      </c>
       <c r="BG2" s="35">
-        <v>8955000989</v>
+        <v>7867000875</v>
       </c>
       <c r="BH2" s="25">
         <v>36526</v>
@@ -1772,151 +1568,130 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="BK2" s="29" t="s">
         <v>130</v>
-      </c>
-      <c r="BK2" s="29" t="s">
-        <v>131</v>
       </c>
       <c r="BL2" s="36">
         <v>32875</v>
       </c>
       <c r="BM2" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BN2" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="BO2" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="BP2" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ2" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="BP2" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" s="24" t="s">
+      <c r="BR2" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="BS2" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BT2" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BU2" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="BR2" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="BS2" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="BT2" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="BU2" s="38" t="s">
+      <c r="BV2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="BV2" s="38" t="s">
+      <c r="BW2" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="BW2" s="24" t="s">
+      <c r="BX2" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="BX2" s="18" t="s">
+      <c r="BY2" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="BY2" s="24" t="s">
+      <c r="BZ2" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="BZ2" s="24" t="s">
+      <c r="CA2" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="CA2" s="24" t="s">
+      <c r="CB2" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="CB2" s="24" t="s">
+      <c r="CC2" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="CD2" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="CE2" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="CF2" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="CC2" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="CD2" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="CE2" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="CF2" s="24" t="s">
+      <c r="CG2" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="CG2" s="24" t="s">
-        <v>143</v>
-      </c>
       <c r="CH2" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CI2" s="40">
         <v>100</v>
       </c>
       <c r="CJ2" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CK2" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="CK2" s="24" t="s">
+      <c r="CL2" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="CM2" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="CL2" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="CM2" s="24" t="s">
+      <c r="CN2" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="CN2" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="CO2" s="41">
-        <v>500</v>
-      </c>
-      <c r="CP2" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="CQ2" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="CR2" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="CS2" s="36" t="s">
-        <v>111</v>
+      <c r="CO2" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="CP2" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="CQ2" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="CR2" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="CS2" s="30" t="s">
+        <v>110</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="CU2" s="40">
-        <v>1234055</v>
-      </c>
-      <c r="CV2" s="40">
-        <v>123456055</v>
+        <v>110</v>
+      </c>
+      <c r="CU2" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 Z2 X2 U2 I2:J2 CC2 BW2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="W2" r:id="rId1"/>
+    <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{59C643C9-9EC0-4514-AB9A-37245B438818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="228">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -316,12 +301,24 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>Test failed for 'Zemlak Dangelo' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_MK/WorkdayFailedScreenshot/2025-03-25T07-32-16-202Z.png</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
   </si>
   <si>
     <t>Hungary</t>
   </si>
   <si>
+    <t>Dangelo</t>
+  </si>
+  <si>
+    <t>Zemlak</t>
+  </si>
+  <si>
     <t>(061)2123123</t>
   </si>
   <si>
@@ -382,7 +379,7 @@
     <t>Automation Comments here….</t>
   </si>
   <si>
-    <t>94 Retail Operatives </t>
+    <t xml:space="preserve">94 Retail Operatives </t>
   </si>
   <si>
     <t>16 Men’s Accessories</t>
@@ -524,13 +521,16 @@
     <t>Test_3</t>
   </si>
   <si>
+    <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
+  </si>
+  <si>
     <t>Auto 20102024 232148</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
   </si>
   <si>
-    <t>92 Retail Management </t>
+    <t xml:space="preserve">92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -699,65 +699,62 @@
   </si>
   <si>
     <t>666666133</t>
-  </si>
-  <si>
-    <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -769,13 +766,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,7 +784,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -801,91 +798,51 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1307,9 +1264,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CV17"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="18.81640625" customWidth="1"/>
@@ -1356,7 +1313,7 @@
     <col min="99" max="99" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1655,90 +1612,98 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:100" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="87.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>96</v>
+      </c>
       <c r="D2" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+        <v>98</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>100</v>
+      </c>
       <c r="H2" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K2" s="19">
-        <f t="shared" ref="K2:K15" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="K2:K15" si="0">TODAY()-31</f>
         <v>45709</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P2" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="T2" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="U2" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="Q2" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="S2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="T2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="V2" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y15" ca="1" si="1">K2</f>
+        <f t="shared" ref="Y2:Y15" si="1">K2</f>
         <v>45709</v>
       </c>
       <c r="Z2" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB2" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AC2" s="29" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AD2" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE2" s="20">
         <v>846</v>
@@ -1750,85 +1715,85 @@
         <v>40</v>
       </c>
       <c r="AH2" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI2" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ2" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK2" s="31">
-        <f t="shared" ref="AK2:AK15" ca="1" si="2">Y2+90</f>
+        <f t="shared" ref="AK2:AK15" si="2">Y2+90</f>
         <v>45799</v>
       </c>
       <c r="AL2" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM2" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN2" s="29" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AO2" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP2" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ2" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR2" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS2" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT2" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU2" s="32" t="str">
         <f t="shared" ref="AU2:AU15" si="3">AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW2" s="33">
-        <f t="shared" ref="AW2:AW15" ca="1" si="4">Y2-1</f>
+        <f t="shared" ref="AW2:AW15" si="4">Y2-1</f>
         <v>45708</v>
       </c>
       <c r="AX2" s="33">
-        <f t="shared" ref="AX2:AX15" ca="1" si="5">Y2-1</f>
+        <f t="shared" ref="AX2:AX15" si="5">Y2-1</f>
         <v>45708</v>
       </c>
       <c r="AY2" s="34">
-        <f t="shared" ref="AY2:AY7" ca="1" si="6">AJ2</f>
+        <f t="shared" ref="AY2:AY7" si="6">AJ2</f>
         <v>46105</v>
       </c>
       <c r="AZ2" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA2" s="24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BB2" s="35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BC2" s="25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BD2" s="25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BE2" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF2" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG2" s="36">
         <v>5555000018</v>
@@ -1840,159 +1805,159 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK2" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL2" s="37">
         <v>32875</v>
       </c>
       <c r="BM2" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN2" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO2" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP2" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ2" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR2" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS2" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU2" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV2" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW2" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX2" s="18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BY2" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ2" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA2" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB2" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC2" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="CB2" s="24" t="s">
+      <c r="CD2" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC2" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD2" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE2" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF2" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG2" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH2" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI2" s="41">
         <v>100</v>
       </c>
       <c r="CJ2" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK2" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL2" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM2" s="24" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="CN2" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP2" s="42" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ2" s="37" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CU2" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K3" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P3" s="43" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q3" s="18">
         <v>123</v>
@@ -2001,41 +1966,41 @@
         <v>1046</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T3" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U3" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V3" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA3" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB3" s="44" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC3" s="39" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AD3" s="45" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE3" s="20">
         <v>846</v>
@@ -2047,72 +2012,72 @@
         <v>10</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI3" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ3" s="46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK3" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL3" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM3" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN3" s="39" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AO3" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP3" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ3" s="18" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AR3" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS3" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT3" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU3" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW3" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX3" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
-      <c r="AY3" s="34" t="str">
+      <c r="AY3" s="34">
         <f t="shared" si="6"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AZ3" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB3" s="35" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="BC3" s="25">
         <v>36526</v>
@@ -2121,10 +2086,10 @@
         <v>51136</v>
       </c>
       <c r="BE3" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF3" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG3" s="36">
         <v>5555000019</v>
@@ -2136,113 +2101,113 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL3" s="37">
         <v>32875</v>
       </c>
       <c r="BM3" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN3" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO3" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP3" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ3" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR3" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS3" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT3" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU3" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV3" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW3" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX3" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY3" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ3" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA3" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB3" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC3" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB3" s="24" t="s">
+      <c r="CD3" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC3" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE3" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF3" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG3" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH3" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI3" s="41">
         <v>100</v>
       </c>
       <c r="CJ3" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK3" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL3" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM3" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN3" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO3" s="30" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="CP3" s="30" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="CQ3" s="42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CR3" s="48">
-        <f ca="1">TODAY()-1500</f>
+        <f>TODAY()-1500</f>
         <v>44240</v>
       </c>
       <c r="CS3" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT3" s="41">
         <v>1234022</v>
@@ -2252,42 +2217,42 @@
       </c>
       <c r="CV3" s="41"/>
     </row>
-    <row r="4" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K4" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N4" s="18">
         <v>1</v>
       </c>
       <c r="O4" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P4" s="49">
         <v>3</v>
@@ -2299,41 +2264,41 @@
         <v>1046</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U4" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V4" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W4" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X4" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y4" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA4" s="27" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AB4" s="32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC4" s="29" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AD4" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE4" s="20">
         <v>846</v>
@@ -2345,58 +2310,58 @@
         <v>10</v>
       </c>
       <c r="AH4" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI4" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ4" s="46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK4" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL4" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM4" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN4" s="39" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO4" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP4" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ4" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR4" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS4" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT4" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU4" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV4" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW4" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX4" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY4" s="50" t="str">
@@ -2404,13 +2369,13 @@
         <v>N/A</v>
       </c>
       <c r="AZ4" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA4" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB4" s="35" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="BC4" s="25">
         <v>36526</v>
@@ -2419,10 +2384,10 @@
         <v>51136</v>
       </c>
       <c r="BE4" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF4" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG4" s="36">
         <v>5555000020</v>
@@ -2434,112 +2399,112 @@
         <v>51136</v>
       </c>
       <c r="BJ4" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK4" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL4" s="37">
         <v>32875</v>
       </c>
       <c r="BM4" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN4" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO4" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP4" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="BQ4" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BS4" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BT4" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BU4" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="BV4" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="BW4" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="BX4" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY4" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="BZ4" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="CA4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CB4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CC4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CE4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CF4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CG4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CH4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CI4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="CJ4" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="CK4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="CL4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="CM4" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="CN4" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="CO4" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="CP4" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="CQ4" s="42" t="s">
         <v>110</v>
-      </c>
-      <c r="BQ4" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="BR4" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="BS4" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT4" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="BU4" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="BV4" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="BW4" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="BX4" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="BY4" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="BZ4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="CA4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CB4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CC4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CD4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CE4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CF4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CG4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CI4" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="CJ4" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="CK4" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="CL4" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="CM4" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="CN4" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="CO4" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="CP4" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="CQ4" s="42" t="s">
-        <v>106</v>
       </c>
       <c r="CR4" s="48">
         <v>31048</v>
       </c>
       <c r="CS4" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT4" s="41">
         <v>1234011</v>
@@ -2549,45 +2514,45 @@
       </c>
       <c r="CV4" s="41"/>
     </row>
-    <row r="5" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K5" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O5" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q5" s="18">
         <v>123</v>
@@ -2596,41 +2561,41 @@
         <v>1046</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U5" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V5" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W5" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X5" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y5" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z5" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA5" s="27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AB5" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC5" s="51" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AD5" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE5" s="20">
         <v>846</v>
@@ -2642,73 +2607,73 @@
         <v>40</v>
       </c>
       <c r="AH5" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI5" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ5" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK5" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL5" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM5" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN5" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO5" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP5" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ5" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR5" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AS5" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT5" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU5" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV5" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW5" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX5" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY5" s="34">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" si="6"/>
         <v>46105</v>
       </c>
       <c r="AZ5" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA5" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB5" s="35" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="BC5" s="25">
         <v>36526</v>
@@ -2717,10 +2682,10 @@
         <v>51136</v>
       </c>
       <c r="BE5" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF5" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG5" s="36">
         <v>5555000021</v>
@@ -2732,112 +2697,112 @@
         <v>51136</v>
       </c>
       <c r="BJ5" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK5" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL5" s="37">
         <v>32875</v>
       </c>
       <c r="BM5" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN5" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO5" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP5" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ5" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR5" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS5" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT5" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU5" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV5" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW5" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX5" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY5" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ5" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA5" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB5" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC5" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB5" s="24" t="s">
+      <c r="CD5" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC5" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD5" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE5" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF5" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG5" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH5" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI5" s="41">
         <v>100</v>
       </c>
       <c r="CJ5" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK5" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL5" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM5" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN5" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO5" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP5" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ5" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR5" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS5" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT5" s="41">
         <v>1234015</v>
@@ -2846,45 +2811,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="6" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K6" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q6" s="18">
         <v>123</v>
@@ -2893,41 +2858,41 @@
         <v>1046</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U6" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V6" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X6" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y6" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z6" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA6" s="27" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AB6" s="54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC6" s="51" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AD6" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE6" s="20">
         <v>846</v>
@@ -2939,72 +2904,72 @@
         <v>35</v>
       </c>
       <c r="AH6" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI6" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ6" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK6" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL6" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM6" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN6" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO6" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP6" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ6" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS6" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT6" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU6" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV6" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW6" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX6" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
-      <c r="AY6" s="34" t="str">
+      <c r="AY6" s="34">
         <f t="shared" si="6"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AZ6" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA6" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB6" s="35" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="BC6" s="25">
         <v>36526</v>
@@ -3013,10 +2978,10 @@
         <v>51136</v>
       </c>
       <c r="BE6" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF6" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG6" s="36">
         <v>5555000022</v>
@@ -3028,112 +2993,112 @@
         <v>51136</v>
       </c>
       <c r="BJ6" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK6" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL6" s="37">
         <v>32875</v>
       </c>
       <c r="BM6" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN6" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO6" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP6" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ6" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR6" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS6" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BT6" s="30">
         <v>10</v>
       </c>
       <c r="BU6" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV6" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW6" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX6" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY6" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ6" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA6" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB6" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC6" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB6" s="24" t="s">
+      <c r="CD6" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC6" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD6" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE6" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF6" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG6" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH6" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI6" s="41">
         <v>100</v>
       </c>
       <c r="CJ6" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK6" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL6" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM6" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN6" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO6" s="32" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="CP6" s="30" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="CQ6" s="42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CR6" s="48">
         <v>31048</v>
       </c>
       <c r="CS6" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT6" s="41">
         <v>1234015</v>
@@ -3142,45 +3107,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="7" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K7" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q7" s="18">
         <v>123</v>
@@ -3189,41 +3154,41 @@
         <v>1046</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U7" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V7" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W7" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X7" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y7" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z7" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA7" s="27" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AB7" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC7" s="51" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AD7" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE7" s="20">
         <v>846</v>
@@ -3235,73 +3200,73 @@
         <v>40</v>
       </c>
       <c r="AH7" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI7" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ7" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK7" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL7" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM7" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN7" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO7" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP7" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ7" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS7" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT7" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU7" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV7" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW7" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX7" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY7" s="34">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" si="6"/>
         <v>46105</v>
       </c>
       <c r="AZ7" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA7" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB7" s="35" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="BC7" s="25">
         <v>36526</v>
@@ -3310,10 +3275,10 @@
         <v>51136</v>
       </c>
       <c r="BE7" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF7" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG7" s="36">
         <v>5555000023</v>
@@ -3325,112 +3290,112 @@
         <v>51136</v>
       </c>
       <c r="BJ7" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK7" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL7" s="37">
         <v>32875</v>
       </c>
       <c r="BM7" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN7" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO7" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP7" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ7" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR7" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS7" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT7" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU7" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV7" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW7" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX7" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY7" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ7" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA7" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB7" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC7" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB7" s="24" t="s">
+      <c r="CD7" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC7" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD7" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE7" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF7" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG7" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH7" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI7" s="41">
         <v>100</v>
       </c>
       <c r="CJ7" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK7" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL7" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM7" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN7" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO7" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP7" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ7" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR7" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS7" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT7" s="41">
         <v>1234015</v>
@@ -3439,45 +3404,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="8" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K8" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P8" s="49" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q8" s="18">
         <v>123</v>
@@ -3486,41 +3451,41 @@
         <v>1046</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U8" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V8" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W8" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X8" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y8" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z8" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA8" s="27" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AB8" s="54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC8" s="51" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AD8" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE8" s="20">
         <v>846</v>
@@ -3532,71 +3497,71 @@
         <v>30</v>
       </c>
       <c r="AH8" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI8" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ8" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK8" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL8" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM8" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN8" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO8" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP8" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ8" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR8" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AS8" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT8" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU8" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV8" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW8" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX8" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY8" s="34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AZ8" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA8" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB8" s="35" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="BC8" s="25">
         <v>36526</v>
@@ -3605,10 +3570,10 @@
         <v>51136</v>
       </c>
       <c r="BE8" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF8" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG8" s="36">
         <v>5555000024</v>
@@ -3620,113 +3585,113 @@
         <v>51136</v>
       </c>
       <c r="BJ8" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK8" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL8" s="37">
         <v>32875</v>
       </c>
       <c r="BM8" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN8" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO8" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP8" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ8" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR8" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS8" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT8" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU8" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV8" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW8" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX8" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY8" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ8" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA8" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB8" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC8" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB8" s="24" t="s">
+      <c r="CD8" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC8" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD8" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE8" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF8" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG8" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH8" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI8" s="41">
         <v>100</v>
       </c>
       <c r="CJ8" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK8" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL8" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM8" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN8" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO8" s="30" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="CP8" s="30" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="CQ8" s="42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CR8" s="48">
-        <f ca="1">TODAY()-1500</f>
+        <f>TODAY()-1500</f>
         <v>44240</v>
       </c>
       <c r="CS8" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT8" s="41">
         <v>1234015</v>
@@ -3735,45 +3700,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="9" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K9" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q9" s="18">
         <v>123</v>
@@ -3782,41 +3747,41 @@
         <v>1046</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U9" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V9" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W9" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X9" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y9" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z9" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA9" s="27" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AB9" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC9" s="51" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AD9" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE9" s="20">
         <v>846</v>
@@ -3828,73 +3793,73 @@
         <v>40</v>
       </c>
       <c r="AH9" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI9" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ9" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK9" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL9" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM9" s="29" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN9" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO9" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP9" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ9" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR9" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS9" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT9" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU9" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV9" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW9" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX9" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY9" s="34">
-        <f ca="1">AJ9</f>
+        <f>AJ9</f>
         <v>46105</v>
       </c>
       <c r="AZ9" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA9" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB9" s="35" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="BC9" s="25">
         <v>36526</v>
@@ -3903,10 +3868,10 @@
         <v>51136</v>
       </c>
       <c r="BE9" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF9" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG9" s="36">
         <v>5555000025</v>
@@ -3918,112 +3883,112 @@
         <v>51136</v>
       </c>
       <c r="BJ9" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK9" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL9" s="37">
         <v>32875</v>
       </c>
       <c r="BM9" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN9" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO9" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP9" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ9" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR9" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS9" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT9" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU9" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV9" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW9" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX9" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY9" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ9" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA9" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB9" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC9" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB9" s="24" t="s">
+      <c r="CD9" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC9" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD9" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE9" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF9" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG9" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH9" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI9" s="41">
         <v>100</v>
       </c>
       <c r="CJ9" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK9" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL9" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM9" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN9" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO9" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP9" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ9" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR9" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS9" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT9" s="41">
         <v>1234015</v>
@@ -4032,45 +3997,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="10" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K10" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O10" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q10" s="18">
         <v>123</v>
@@ -4079,41 +4044,41 @@
         <v>1046</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U10" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V10" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W10" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X10" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y10" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z10" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA10" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB10" s="54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC10" s="51" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AD10" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE10" s="20">
         <v>846</v>
@@ -4125,71 +4090,71 @@
         <v>20</v>
       </c>
       <c r="AH10" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI10" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ10" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK10" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL10" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM10" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN10" s="51" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AO10" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP10" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ10" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR10" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS10" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT10" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU10" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV10" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW10" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX10" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY10" s="34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AZ10" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA10" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB10" s="35" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="BC10" s="25">
         <v>36526</v>
@@ -4198,10 +4163,10 @@
         <v>51136</v>
       </c>
       <c r="BE10" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF10" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG10" s="36">
         <v>5555000026</v>
@@ -4213,112 +4178,112 @@
         <v>51136</v>
       </c>
       <c r="BJ10" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK10" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL10" s="37">
         <v>32875</v>
       </c>
       <c r="BM10" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN10" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO10" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP10" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ10" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR10" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS10" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT10" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU10" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV10" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW10" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX10" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY10" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ10" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA10" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB10" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC10" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB10" s="24" t="s">
+      <c r="CD10" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC10" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD10" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE10" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF10" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG10" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH10" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI10" s="41">
         <v>100</v>
       </c>
       <c r="CJ10" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK10" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL10" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM10" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN10" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO10" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP10" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ10" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR10" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS10" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT10" s="41">
         <v>1234015</v>
@@ -4327,45 +4292,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="11" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K11" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O11" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P11" s="49" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q11" s="18">
         <v>123</v>
@@ -4374,41 +4339,41 @@
         <v>1046</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U11" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V11" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W11" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X11" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y11" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z11" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA11" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB11" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC11" s="51" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AD11" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE11" s="20">
         <v>846</v>
@@ -4420,73 +4385,73 @@
         <v>40</v>
       </c>
       <c r="AH11" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI11" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ11" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK11" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL11" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM11" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN11" s="51" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AO11" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP11" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AQ11" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR11" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AS11" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT11" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU11" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV11" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW11" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX11" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY11" s="34">
-        <f ca="1">AJ11</f>
+        <f>AJ11</f>
         <v>46105</v>
       </c>
       <c r="AZ11" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA11" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB11" s="35" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="BC11" s="25">
         <v>36526</v>
@@ -4495,10 +4460,10 @@
         <v>51136</v>
       </c>
       <c r="BE11" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF11" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG11" s="36">
         <v>5555000027</v>
@@ -4510,113 +4475,113 @@
         <v>51136</v>
       </c>
       <c r="BJ11" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK11" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL11" s="37">
         <v>32875</v>
       </c>
       <c r="BM11" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN11" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO11" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP11" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ11" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR11" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS11" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT11" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU11" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV11" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW11" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX11" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY11" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ11" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA11" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB11" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC11" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB11" s="24" t="s">
+      <c r="CD11" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC11" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD11" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE11" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF11" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG11" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH11" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI11" s="41">
         <v>100</v>
       </c>
       <c r="CJ11" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK11" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL11" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM11" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN11" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO11" s="30" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="CP11" s="30" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="CQ11" s="42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CR11" s="48">
-        <f ca="1">TODAY()-1500</f>
+        <f>TODAY()-1500</f>
         <v>44240</v>
       </c>
       <c r="CS11" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT11" s="41">
         <v>1234015</v>
@@ -4625,45 +4590,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="12" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K12" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O12" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P12" s="49" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q12" s="18">
         <v>123</v>
@@ -4672,41 +4637,41 @@
         <v>1046</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U12" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V12" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W12" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X12" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y12" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z12" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA12" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB12" s="54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC12" s="51" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AD12" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE12" s="20">
         <v>846</v>
@@ -4718,72 +4683,72 @@
         <v>25</v>
       </c>
       <c r="AH12" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ12" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK12" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL12" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM12" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN12" s="51" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AO12" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP12" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ12" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR12" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS12" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT12" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU12" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV12" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW12" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX12" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
-      <c r="AY12" s="34" t="str">
+      <c r="AY12" s="34">
         <f>AJ12</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AZ12" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA12" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB12" s="35" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="BC12" s="25">
         <v>36526</v>
@@ -4792,10 +4757,10 @@
         <v>51136</v>
       </c>
       <c r="BE12" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF12" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG12" s="36">
         <v>5555000028</v>
@@ -4807,112 +4772,112 @@
         <v>51136</v>
       </c>
       <c r="BJ12" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK12" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL12" s="37">
         <v>32875</v>
       </c>
       <c r="BM12" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN12" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO12" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP12" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ12" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR12" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS12" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT12" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU12" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV12" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW12" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX12" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY12" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ12" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA12" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB12" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC12" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB12" s="24" t="s">
+      <c r="CD12" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC12" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD12" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE12" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF12" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG12" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH12" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI12" s="41">
         <v>100</v>
       </c>
       <c r="CJ12" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK12" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL12" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM12" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN12" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO12" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP12" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ12" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR12" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS12" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT12" s="41">
         <v>1234015</v>
@@ -4921,45 +4886,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="13" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K13" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M13" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P13" s="49" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q13" s="18">
         <v>123</v>
@@ -4968,41 +4933,41 @@
         <v>1046</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U13" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V13" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W13" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X13" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y13" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z13" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA13" s="27" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AB13" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC13" s="51" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AD13" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE13" s="20">
         <v>846</v>
@@ -5014,73 +4979,73 @@
         <v>40</v>
       </c>
       <c r="AH13" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ13" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK13" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL13" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM13" s="29" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN13" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO13" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP13" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AQ13" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR13" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS13" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT13" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU13" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV13" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW13" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX13" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY13" s="34">
-        <f ca="1">AJ13</f>
+        <f>AJ13</f>
         <v>46105</v>
       </c>
       <c r="AZ13" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA13" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB13" s="35" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="BC13" s="25">
         <v>36526</v>
@@ -5089,10 +5054,10 @@
         <v>51136</v>
       </c>
       <c r="BE13" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF13" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG13" s="36">
         <v>5555000029</v>
@@ -5104,112 +5069,112 @@
         <v>51136</v>
       </c>
       <c r="BJ13" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK13" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL13" s="37">
         <v>32875</v>
       </c>
       <c r="BM13" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN13" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO13" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP13" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ13" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR13" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS13" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT13" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU13" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV13" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW13" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX13" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY13" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ13" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA13" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB13" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC13" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB13" s="24" t="s">
+      <c r="CD13" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC13" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD13" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE13" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF13" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG13" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH13" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI13" s="41">
         <v>100</v>
       </c>
       <c r="CJ13" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK13" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL13" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM13" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN13" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO13" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP13" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ13" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR13" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS13" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT13" s="41">
         <v>1234015</v>
@@ -5218,45 +5183,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="14" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K14" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q14" s="18">
         <v>123</v>
@@ -5265,41 +5230,41 @@
         <v>1046</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U14" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V14" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W14" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X14" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y14" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z14" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA14" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AB14" s="54" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AC14" s="29" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AD14" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AE14" s="20">
         <v>846</v>
@@ -5311,72 +5276,72 @@
         <v>15</v>
       </c>
       <c r="AH14" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AI14" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ14" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AK14" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL14" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM14" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AN14" s="51" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AO14" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP14" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AQ14" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR14" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AS14" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT14" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU14" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV14" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW14" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX14" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
-      <c r="AY14" s="34" t="str">
+      <c r="AY14" s="34">
         <f>AJ14</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AZ14" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA14" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB14" s="35" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="BC14" s="25">
         <v>36526</v>
@@ -5385,10 +5350,10 @@
         <v>51136</v>
       </c>
       <c r="BE14" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF14" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG14" s="36">
         <v>5555000030</v>
@@ -5400,112 +5365,112 @@
         <v>51136</v>
       </c>
       <c r="BJ14" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK14" s="29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BL14" s="37">
         <v>32875</v>
       </c>
       <c r="BM14" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN14" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO14" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP14" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ14" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR14" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS14" s="29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BT14" s="30">
         <v>10</v>
       </c>
       <c r="BU14" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV14" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW14" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX14" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY14" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ14" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA14" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB14" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC14" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB14" s="24" t="s">
+      <c r="CD14" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC14" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD14" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE14" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF14" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG14" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH14" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI14" s="41">
         <v>100</v>
       </c>
       <c r="CJ14" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK14" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL14" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM14" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN14" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO14" s="32" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="CP14" s="30" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="CQ14" s="42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CR14" s="48">
         <v>31048</v>
       </c>
       <c r="CS14" s="30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="CT14" s="41">
         <v>1234015</v>
@@ -5514,45 +5479,45 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="15" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
       <c r="H15" s="17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K15" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45709</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q15" s="18">
         <v>123</v>
@@ -5561,41 +5526,41 @@
         <v>1046</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U15" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V15" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W15" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X15" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y15" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45709</v>
       </c>
       <c r="Z15" s="18" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA15" s="27" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AB15" s="44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC15" s="51" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AD15" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AE15" s="20">
         <v>846</v>
@@ -5607,73 +5572,73 @@
         <v>40</v>
       </c>
       <c r="AH15" s="29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AI15" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AJ15" s="31">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46105</v>
       </c>
       <c r="AK15" s="31">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AL15" s="18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AM15" s="29" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN15" s="51" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AO15" s="18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AP15" s="32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AQ15" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AR15" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AS15" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AT15" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AU15" s="32" t="str">
         <f t="shared" si="3"/>
         <v>Fixed Term</v>
       </c>
       <c r="AV15" s="25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AW15" s="33">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>45708</v>
       </c>
       <c r="AX15" s="33">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>45708</v>
       </c>
       <c r="AY15" s="34">
-        <f ca="1">AJ15</f>
+        <f>AJ15</f>
         <v>46105</v>
       </c>
       <c r="AZ15" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA15" s="24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="BB15" s="35" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="BC15" s="25">
         <v>36526</v>
@@ -5682,10 +5647,10 @@
         <v>51136</v>
       </c>
       <c r="BE15" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF15" s="24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG15" s="36">
         <v>5555000031</v>
@@ -5697,112 +5662,112 @@
         <v>51136</v>
       </c>
       <c r="BJ15" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BK15" s="29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BL15" s="37">
         <v>32875</v>
       </c>
       <c r="BM15" s="38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN15" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BO15" s="39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BP15" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BQ15" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BR15" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS15" s="29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BT15" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="BU15" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BV15" s="39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="BW15" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BX15" s="47" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="BY15" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BZ15" s="24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="CA15" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB15" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC15" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="CB15" s="24" t="s">
+      <c r="CD15" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="CC15" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD15" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="CE15" s="24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="CF15" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CG15" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CH15" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="CI15" s="41">
         <v>100</v>
       </c>
       <c r="CJ15" s="24" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CK15" s="24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CL15" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM15" s="24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN15" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CO15" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CP15" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CQ15" s="52" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CR15" s="53" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CS15" s="30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CT15" s="41">
         <v>1234015</v>
@@ -5811,44 +5776,98 @@
         <v>123456005</v>
       </c>
     </row>
-    <row r="16" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="14.5" customHeight="1" spans="36:36" x14ac:dyDescent="0.25">
       <c r="AJ16" s="55"/>
     </row>
-    <row r="17" spans="36:36" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="14.5" customHeight="1" spans="36:36" x14ac:dyDescent="0.25">
       <c r="AJ17" s="55"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV10:AV15 Z10:Z15 X10:X15 U10:U15 I10:J15 CC10:CC15 BW10:BW15" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV10:AV15">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 Z2 X2 U2 I2:J2 CC2 BW2" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV15 Z3:Z15 X3:X15 U3:U15 I3:J15 CC3 BW3:BW15" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV15">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC5:CC15" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW10:BW15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3:BW15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC10:CC15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC5:CC15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:J15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U10:U15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z10:Z15">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z15">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="W3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="W4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="W5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="W6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="W7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="W8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="W9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="W10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="W11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="W12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="W13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="W14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="W15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="W2" r:id="rId1"/>
+    <hyperlink ref="W3" r:id="rId2"/>
+    <hyperlink ref="W4" r:id="rId3"/>
+    <hyperlink ref="W5" r:id="rId4"/>
+    <hyperlink ref="W6" r:id="rId5"/>
+    <hyperlink ref="W7" r:id="rId6"/>
+    <hyperlink ref="W8" r:id="rId7"/>
+    <hyperlink ref="W9" r:id="rId8"/>
+    <hyperlink ref="W10" r:id="rId9"/>
+    <hyperlink ref="W11" r:id="rId10"/>
+    <hyperlink ref="W12" r:id="rId11"/>
+    <hyperlink ref="W13" r:id="rId12"/>
+    <hyperlink ref="W14" r:id="rId13"/>
+    <hyperlink ref="W15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId15"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="231">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -301,7 +301,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>Test failed for 'Zemlak Dangelo' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_MK/WorkdayFailedScreenshot/2025-03-25T07-32-16-202Z.png</t>
+    <t>Test failed for 'Brock Kulas' Employee:{undefined}TypeError: Cannot read properties of undefined (reading 'toLowerCase')</t>
   </si>
   <si>
     <t>Failed</t>
@@ -313,10 +313,10 @@
     <t>Hungary</t>
   </si>
   <si>
-    <t>Dangelo</t>
-  </si>
-  <si>
-    <t>Zemlak</t>
+    <t>Brock</t>
+  </si>
+  <si>
+    <t>Kulas</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -404,7 +404,7 @@
     <t>Social Security</t>
   </si>
   <si>
-    <t>666666120</t>
+    <t>666666150</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -473,6 +473,18 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Ottilie Kuphal' Employee:{10698281}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByRole('button', { name: 'Approve' })[22m
+</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Prohaska</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
@@ -497,7 +509,7 @@
     <t>Social Security (TAJ) Number</t>
   </si>
   <si>
-    <t>666666121</t>
+    <t>666966123</t>
   </si>
   <si>
     <t>Female</t>
@@ -1645,7 +1657,7 @@
       </c>
       <c r="K2" s="19">
         <f t="shared" ref="K2:K15" si="0">TODAY()-31</f>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L2" s="20" t="s">
         <v>98</v>
@@ -1688,7 +1700,7 @@
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y15" si="1">K2</f>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z2" s="18" t="s">
         <v>113</v>
@@ -1722,11 +1734,11 @@
       </c>
       <c r="AJ2" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK2" s="31">
         <f t="shared" ref="AK2:AK15" si="2">Y2+90</f>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL2" s="18" t="s">
         <v>120</v>
@@ -1764,15 +1776,15 @@
       </c>
       <c r="AW2" s="33">
         <f t="shared" ref="AW2:AW15" si="4">Y2-1</f>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX2" s="33">
         <f t="shared" ref="AX2:AX15" si="5">Y2-1</f>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY2" s="34">
         <f t="shared" ref="AY2:AY7" si="6">AJ2</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ2" s="24" t="s">
         <v>98</v>
@@ -1796,7 +1808,7 @@
         <v>132</v>
       </c>
       <c r="BG2" s="36">
-        <v>5555000018</v>
+        <v>5555000040</v>
       </c>
       <c r="BH2" s="25">
         <v>36526</v>
@@ -1923,14 +1935,24 @@
       <c r="A3" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>96</v>
+      </c>
       <c r="D3" s="14" t="s">
         <v>97</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
+      <c r="F3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" t="s">
+        <v>154</v>
+      </c>
       <c r="H3" s="17" t="s">
         <v>101</v>
       </c>
@@ -1942,7 +1964,7 @@
       </c>
       <c r="K3" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L3" s="20" t="s">
         <v>98</v>
@@ -1951,13 +1973,13 @@
         <v>104</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O3" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P3" s="43" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q3" s="18">
         <v>123</v>
@@ -1985,7 +2007,7 @@
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z3" s="18" t="s">
         <v>113</v>
@@ -1994,13 +2016,13 @@
         <v>114</v>
       </c>
       <c r="AB3" s="44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC3" s="39" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AD3" s="45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE3" s="20">
         <v>846</v>
@@ -2012,7 +2034,7 @@
         <v>10</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI3" s="20" t="s">
         <v>119</v>
@@ -2022,7 +2044,7 @@
       </c>
       <c r="AK3" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL3" s="18" t="s">
         <v>120</v>
@@ -2031,7 +2053,7 @@
         <v>121</v>
       </c>
       <c r="AN3" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AO3" s="18" t="s">
         <v>123</v>
@@ -2043,7 +2065,7 @@
         <v>124</v>
       </c>
       <c r="AR3" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AS3" s="25" t="s">
         <v>114</v>
@@ -2060,11 +2082,11 @@
       </c>
       <c r="AW3" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX3" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY3" s="34">
         <f t="shared" si="6"/>
@@ -2074,10 +2096,10 @@
         <v>98</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB3" s="35" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="BC3" s="25">
         <v>36526</v>
@@ -2092,7 +2114,7 @@
         <v>132</v>
       </c>
       <c r="BG3" s="36">
-        <v>5555000019</v>
+        <v>5554000021</v>
       </c>
       <c r="BH3" s="25">
         <v>36526</v>
@@ -2104,7 +2126,7 @@
         <v>133</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL3" s="37">
         <v>32875</v>
@@ -2143,7 +2165,7 @@
         <v>139</v>
       </c>
       <c r="BX3" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY3" s="24" t="s">
         <v>141</v>
@@ -2188,26 +2210,26 @@
         <v>98</v>
       </c>
       <c r="CM3" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN3" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO3" s="30" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="CP3" s="30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="CQ3" s="42" t="s">
         <v>110</v>
       </c>
       <c r="CR3" s="48">
         <f>TODAY()-1500</f>
-        <v>44240</v>
+        <v>44250</v>
       </c>
       <c r="CS3" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT3" s="41">
         <v>1234022</v>
@@ -2219,10 +2241,10 @@
     </row>
     <row r="4" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>98</v>
@@ -2240,7 +2262,7 @@
       </c>
       <c r="K4" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L4" s="20" t="s">
         <v>98</v>
@@ -2283,22 +2305,22 @@
       </c>
       <c r="Y4" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z4" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA4" s="27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB4" s="32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC4" s="29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AD4" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE4" s="20">
         <v>846</v>
@@ -2310,7 +2332,7 @@
         <v>10</v>
       </c>
       <c r="AH4" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI4" s="20" t="s">
         <v>119</v>
@@ -2320,16 +2342,16 @@
       </c>
       <c r="AK4" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL4" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM4" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN4" s="39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO4" s="18" t="s">
         <v>123</v>
@@ -2358,11 +2380,11 @@
       </c>
       <c r="AW4" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX4" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY4" s="50" t="str">
         <f t="shared" si="6"/>
@@ -2372,10 +2394,10 @@
         <v>98</v>
       </c>
       <c r="BA4" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB4" s="35" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="BC4" s="25">
         <v>36526</v>
@@ -2402,7 +2424,7 @@
         <v>133</v>
       </c>
       <c r="BK4" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL4" s="37">
         <v>32875</v>
@@ -2441,7 +2463,7 @@
         <v>139</v>
       </c>
       <c r="BX4" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY4" s="24" t="s">
         <v>141</v>
@@ -2486,16 +2508,16 @@
         <v>98</v>
       </c>
       <c r="CM4" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN4" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO4" s="32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="CP4" s="30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CQ4" s="42" t="s">
         <v>110</v>
@@ -2504,7 +2526,7 @@
         <v>31048</v>
       </c>
       <c r="CS4" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT4" s="41">
         <v>1234011</v>
@@ -2516,10 +2538,10 @@
     </row>
     <row r="5" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>98</v>
@@ -2537,7 +2559,7 @@
       </c>
       <c r="K5" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L5" s="20" t="s">
         <v>98</v>
@@ -2546,13 +2568,13 @@
         <v>104</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O5" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q5" s="18">
         <v>123</v>
@@ -2580,19 +2602,19 @@
       </c>
       <c r="Y5" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z5" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA5" s="27" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AB5" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC5" s="51" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AD5" s="30" t="s">
         <v>117</v>
@@ -2607,27 +2629,27 @@
         <v>40</v>
       </c>
       <c r="AH5" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI5" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ5" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK5" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL5" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM5" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN5" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO5" s="18" t="s">
         <v>123</v>
@@ -2656,24 +2678,24 @@
       </c>
       <c r="AW5" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX5" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY5" s="34">
         <f t="shared" si="6"/>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ5" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA5" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB5" s="35" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="BC5" s="25">
         <v>36526</v>
@@ -2739,7 +2761,7 @@
         <v>139</v>
       </c>
       <c r="BX5" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY5" s="24" t="s">
         <v>141</v>
@@ -2784,7 +2806,7 @@
         <v>98</v>
       </c>
       <c r="CM5" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN5" s="24" t="s">
         <v>150</v>
@@ -2813,10 +2835,10 @@
     </row>
     <row r="6" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>98</v>
@@ -2834,7 +2856,7 @@
       </c>
       <c r="K6" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L6" s="20" t="s">
         <v>98</v>
@@ -2843,13 +2865,13 @@
         <v>104</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O6" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q6" s="18">
         <v>123</v>
@@ -2877,22 +2899,22 @@
       </c>
       <c r="Y6" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z6" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA6" s="27" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AB6" s="54" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC6" s="51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AD6" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE6" s="20">
         <v>846</v>
@@ -2914,16 +2936,16 @@
       </c>
       <c r="AK6" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL6" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM6" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN6" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO6" s="18" t="s">
         <v>123</v>
@@ -2952,11 +2974,11 @@
       </c>
       <c r="AW6" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX6" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY6" s="34">
         <f t="shared" si="6"/>
@@ -2966,10 +2988,10 @@
         <v>98</v>
       </c>
       <c r="BA6" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB6" s="35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="BC6" s="25">
         <v>36526</v>
@@ -2996,7 +3018,7 @@
         <v>133</v>
       </c>
       <c r="BK6" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL6" s="37">
         <v>32875</v>
@@ -3035,7 +3057,7 @@
         <v>139</v>
       </c>
       <c r="BX6" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY6" s="24" t="s">
         <v>141</v>
@@ -3080,16 +3102,16 @@
         <v>98</v>
       </c>
       <c r="CM6" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN6" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO6" s="32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="CP6" s="30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CQ6" s="42" t="s">
         <v>110</v>
@@ -3098,7 +3120,7 @@
         <v>31048</v>
       </c>
       <c r="CS6" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT6" s="41">
         <v>1234015</v>
@@ -3109,10 +3131,10 @@
     </row>
     <row r="7" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>98</v>
@@ -3130,7 +3152,7 @@
       </c>
       <c r="K7" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L7" s="20" t="s">
         <v>98</v>
@@ -3139,13 +3161,13 @@
         <v>104</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O7" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q7" s="18">
         <v>123</v>
@@ -3173,19 +3195,19 @@
       </c>
       <c r="Y7" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z7" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA7" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AB7" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC7" s="51" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AD7" s="30" t="s">
         <v>117</v>
@@ -3200,27 +3222,27 @@
         <v>40</v>
       </c>
       <c r="AH7" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI7" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ7" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK7" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL7" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM7" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN7" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO7" s="18" t="s">
         <v>123</v>
@@ -3249,24 +3271,24 @@
       </c>
       <c r="AW7" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX7" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY7" s="34">
         <f t="shared" si="6"/>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ7" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA7" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB7" s="35" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="BC7" s="25">
         <v>36526</v>
@@ -3332,7 +3354,7 @@
         <v>139</v>
       </c>
       <c r="BX7" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY7" s="24" t="s">
         <v>141</v>
@@ -3377,7 +3399,7 @@
         <v>98</v>
       </c>
       <c r="CM7" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN7" s="24" t="s">
         <v>150</v>
@@ -3406,10 +3428,10 @@
     </row>
     <row r="8" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>98</v>
@@ -3427,7 +3449,7 @@
       </c>
       <c r="K8" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L8" s="20" t="s">
         <v>98</v>
@@ -3436,13 +3458,13 @@
         <v>104</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O8" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P8" s="49" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q8" s="18">
         <v>123</v>
@@ -3470,22 +3492,22 @@
       </c>
       <c r="Y8" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z8" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA8" s="27" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AB8" s="54" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC8" s="51" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AD8" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE8" s="20">
         <v>846</v>
@@ -3507,16 +3529,16 @@
       </c>
       <c r="AK8" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL8" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM8" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN8" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO8" s="18" t="s">
         <v>123</v>
@@ -3545,11 +3567,11 @@
       </c>
       <c r="AW8" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX8" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY8" s="34" t="s">
         <v>114</v>
@@ -3558,10 +3580,10 @@
         <v>98</v>
       </c>
       <c r="BA8" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB8" s="35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BC8" s="25">
         <v>36526</v>
@@ -3588,7 +3610,7 @@
         <v>133</v>
       </c>
       <c r="BK8" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL8" s="37">
         <v>32875</v>
@@ -3627,7 +3649,7 @@
         <v>139</v>
       </c>
       <c r="BX8" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY8" s="24" t="s">
         <v>141</v>
@@ -3672,26 +3694,26 @@
         <v>98</v>
       </c>
       <c r="CM8" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN8" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO8" s="30" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="CP8" s="30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="CQ8" s="42" t="s">
         <v>110</v>
       </c>
       <c r="CR8" s="48">
         <f>TODAY()-1500</f>
-        <v>44240</v>
+        <v>44250</v>
       </c>
       <c r="CS8" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT8" s="41">
         <v>1234015</v>
@@ -3702,10 +3724,10 @@
     </row>
     <row r="9" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>98</v>
@@ -3723,7 +3745,7 @@
       </c>
       <c r="K9" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L9" s="20" t="s">
         <v>98</v>
@@ -3732,13 +3754,13 @@
         <v>104</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O9" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q9" s="18">
         <v>123</v>
@@ -3766,19 +3788,19 @@
       </c>
       <c r="Y9" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z9" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA9" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AB9" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC9" s="51" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AD9" s="30" t="s">
         <v>117</v>
@@ -3793,27 +3815,27 @@
         <v>40</v>
       </c>
       <c r="AH9" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI9" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ9" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK9" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL9" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM9" s="29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AN9" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO9" s="18" t="s">
         <v>123</v>
@@ -3842,24 +3864,24 @@
       </c>
       <c r="AW9" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX9" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY9" s="34">
         <f>AJ9</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ9" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA9" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB9" s="35" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BC9" s="25">
         <v>36526</v>
@@ -3925,7 +3947,7 @@
         <v>139</v>
       </c>
       <c r="BX9" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY9" s="24" t="s">
         <v>141</v>
@@ -3970,7 +3992,7 @@
         <v>98</v>
       </c>
       <c r="CM9" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN9" s="24" t="s">
         <v>150</v>
@@ -3999,7 +4021,7 @@
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>97</v>
@@ -4020,7 +4042,7 @@
       </c>
       <c r="K10" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L10" s="20" t="s">
         <v>98</v>
@@ -4029,13 +4051,13 @@
         <v>104</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O10" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q10" s="18">
         <v>123</v>
@@ -4063,7 +4085,7 @@
       </c>
       <c r="Y10" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z10" s="18" t="s">
         <v>113</v>
@@ -4072,13 +4094,13 @@
         <v>114</v>
       </c>
       <c r="AB10" s="54" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC10" s="51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AD10" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE10" s="20">
         <v>846</v>
@@ -4100,7 +4122,7 @@
       </c>
       <c r="AK10" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL10" s="18" t="s">
         <v>120</v>
@@ -4109,7 +4131,7 @@
         <v>121</v>
       </c>
       <c r="AN10" s="51" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AO10" s="18" t="s">
         <v>123</v>
@@ -4138,11 +4160,11 @@
       </c>
       <c r="AW10" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX10" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY10" s="34" t="s">
         <v>114</v>
@@ -4151,10 +4173,10 @@
         <v>98</v>
       </c>
       <c r="BA10" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB10" s="35" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="BC10" s="25">
         <v>36526</v>
@@ -4181,7 +4203,7 @@
         <v>133</v>
       </c>
       <c r="BK10" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL10" s="37">
         <v>32875</v>
@@ -4220,7 +4242,7 @@
         <v>139</v>
       </c>
       <c r="BX10" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY10" s="24" t="s">
         <v>141</v>
@@ -4265,7 +4287,7 @@
         <v>98</v>
       </c>
       <c r="CM10" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN10" s="24" t="s">
         <v>150</v>
@@ -4294,7 +4316,7 @@
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>97</v>
@@ -4315,7 +4337,7 @@
       </c>
       <c r="K11" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L11" s="20" t="s">
         <v>98</v>
@@ -4324,13 +4346,13 @@
         <v>104</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O11" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P11" s="49" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q11" s="18">
         <v>123</v>
@@ -4358,7 +4380,7 @@
       </c>
       <c r="Y11" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z11" s="18" t="s">
         <v>113</v>
@@ -4367,10 +4389,10 @@
         <v>114</v>
       </c>
       <c r="AB11" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC11" s="51" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AD11" s="30" t="s">
         <v>117</v>
@@ -4385,18 +4407,18 @@
         <v>40</v>
       </c>
       <c r="AH11" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI11" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ11" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK11" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL11" s="18" t="s">
         <v>120</v>
@@ -4405,7 +4427,7 @@
         <v>121</v>
       </c>
       <c r="AN11" s="51" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AO11" s="18" t="s">
         <v>123</v>
@@ -4434,24 +4456,24 @@
       </c>
       <c r="AW11" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX11" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY11" s="34">
         <f>AJ11</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ11" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA11" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB11" s="35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="BC11" s="25">
         <v>36526</v>
@@ -4517,7 +4539,7 @@
         <v>139</v>
       </c>
       <c r="BX11" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY11" s="24" t="s">
         <v>141</v>
@@ -4562,26 +4584,26 @@
         <v>98</v>
       </c>
       <c r="CM11" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN11" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO11" s="30" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="CP11" s="30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="CQ11" s="42" t="s">
         <v>110</v>
       </c>
       <c r="CR11" s="48">
         <f>TODAY()-1500</f>
-        <v>44240</v>
+        <v>44250</v>
       </c>
       <c r="CS11" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT11" s="41">
         <v>1234015</v>
@@ -4592,7 +4614,7 @@
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>97</v>
@@ -4613,7 +4635,7 @@
       </c>
       <c r="K12" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L12" s="20" t="s">
         <v>98</v>
@@ -4622,13 +4644,13 @@
         <v>104</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O12" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P12" s="49" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q12" s="18">
         <v>123</v>
@@ -4656,7 +4678,7 @@
       </c>
       <c r="Y12" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z12" s="18" t="s">
         <v>113</v>
@@ -4665,13 +4687,13 @@
         <v>114</v>
       </c>
       <c r="AB12" s="54" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC12" s="51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AD12" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE12" s="20">
         <v>846</v>
@@ -4693,7 +4715,7 @@
       </c>
       <c r="AK12" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL12" s="18" t="s">
         <v>120</v>
@@ -4702,7 +4724,7 @@
         <v>121</v>
       </c>
       <c r="AN12" s="51" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO12" s="18" t="s">
         <v>123</v>
@@ -4731,11 +4753,11 @@
       </c>
       <c r="AW12" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX12" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY12" s="34">
         <f>AJ12</f>
@@ -4745,10 +4767,10 @@
         <v>98</v>
       </c>
       <c r="BA12" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB12" s="35" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="BC12" s="25">
         <v>36526</v>
@@ -4775,7 +4797,7 @@
         <v>133</v>
       </c>
       <c r="BK12" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL12" s="37">
         <v>32875</v>
@@ -4814,7 +4836,7 @@
         <v>139</v>
       </c>
       <c r="BX12" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY12" s="24" t="s">
         <v>141</v>
@@ -4859,7 +4881,7 @@
         <v>98</v>
       </c>
       <c r="CM12" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN12" s="24" t="s">
         <v>150</v>
@@ -4888,10 +4910,10 @@
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>98</v>
@@ -4909,7 +4931,7 @@
       </c>
       <c r="K13" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L13" s="20" t="s">
         <v>98</v>
@@ -4918,7 +4940,7 @@
         <v>104</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O13" s="22" t="s">
         <v>106</v>
@@ -4952,19 +4974,19 @@
       </c>
       <c r="Y13" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z13" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA13" s="27" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AB13" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC13" s="51" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD13" s="30" t="s">
         <v>117</v>
@@ -4979,27 +5001,27 @@
         <v>40</v>
       </c>
       <c r="AH13" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI13" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ13" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK13" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL13" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM13" s="29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AN13" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO13" s="18" t="s">
         <v>123</v>
@@ -5028,24 +5050,24 @@
       </c>
       <c r="AW13" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX13" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY13" s="34">
         <f>AJ13</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ13" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA13" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB13" s="35" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="BC13" s="25">
         <v>36526</v>
@@ -5111,7 +5133,7 @@
         <v>139</v>
       </c>
       <c r="BX13" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY13" s="24" t="s">
         <v>141</v>
@@ -5156,7 +5178,7 @@
         <v>98</v>
       </c>
       <c r="CM13" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN13" s="24" t="s">
         <v>150</v>
@@ -5185,7 +5207,7 @@
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>97</v>
@@ -5206,7 +5228,7 @@
       </c>
       <c r="K14" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L14" s="20" t="s">
         <v>98</v>
@@ -5215,13 +5237,13 @@
         <v>104</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O14" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q14" s="18">
         <v>123</v>
@@ -5249,7 +5271,7 @@
       </c>
       <c r="Y14" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z14" s="18" t="s">
         <v>113</v>
@@ -5258,13 +5280,13 @@
         <v>114</v>
       </c>
       <c r="AB14" s="54" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC14" s="29" t="s">
         <v>116</v>
       </c>
       <c r="AD14" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AE14" s="20">
         <v>846</v>
@@ -5286,7 +5308,7 @@
       </c>
       <c r="AK14" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL14" s="18" t="s">
         <v>120</v>
@@ -5295,7 +5317,7 @@
         <v>121</v>
       </c>
       <c r="AN14" s="51" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AO14" s="18" t="s">
         <v>123</v>
@@ -5324,11 +5346,11 @@
       </c>
       <c r="AW14" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX14" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY14" s="34">
         <f>AJ14</f>
@@ -5338,10 +5360,10 @@
         <v>98</v>
       </c>
       <c r="BA14" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB14" s="35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="BC14" s="25">
         <v>36526</v>
@@ -5368,7 +5390,7 @@
         <v>133</v>
       </c>
       <c r="BK14" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BL14" s="37">
         <v>32875</v>
@@ -5407,7 +5429,7 @@
         <v>139</v>
       </c>
       <c r="BX14" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY14" s="24" t="s">
         <v>141</v>
@@ -5452,16 +5474,16 @@
         <v>98</v>
       </c>
       <c r="CM14" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN14" s="24" t="s">
         <v>150</v>
       </c>
       <c r="CO14" s="32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="CP14" s="30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CQ14" s="42" t="s">
         <v>110</v>
@@ -5470,7 +5492,7 @@
         <v>31048</v>
       </c>
       <c r="CS14" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CT14" s="41">
         <v>1234015</v>
@@ -5481,10 +5503,10 @@
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>98</v>
@@ -5502,7 +5524,7 @@
       </c>
       <c r="K15" s="19">
         <f t="shared" si="0"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="L15" s="20" t="s">
         <v>98</v>
@@ -5511,13 +5533,13 @@
         <v>104</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O15" s="22" t="s">
         <v>106</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q15" s="18">
         <v>123</v>
@@ -5545,19 +5567,19 @@
       </c>
       <c r="Y15" s="19">
         <f t="shared" si="1"/>
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="Z15" s="18" t="s">
         <v>113</v>
       </c>
       <c r="AA15" s="27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AB15" s="44" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AC15" s="51" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AD15" s="30" t="s">
         <v>117</v>
@@ -5572,27 +5594,27 @@
         <v>40</v>
       </c>
       <c r="AH15" s="29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI15" s="20" t="s">
         <v>119</v>
       </c>
       <c r="AJ15" s="31">
         <f>TODAY()+365</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AK15" s="31">
         <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45809</v>
       </c>
       <c r="AL15" s="18" t="s">
         <v>120</v>
       </c>
       <c r="AM15" s="29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AN15" s="51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AO15" s="18" t="s">
         <v>123</v>
@@ -5621,24 +5643,24 @@
       </c>
       <c r="AW15" s="33">
         <f t="shared" si="4"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AX15" s="33">
         <f t="shared" si="5"/>
-        <v>45708</v>
+        <v>45718</v>
       </c>
       <c r="AY15" s="34">
         <f>AJ15</f>
-        <v>46105</v>
+        <v>46115</v>
       </c>
       <c r="AZ15" s="24" t="s">
         <v>98</v>
       </c>
       <c r="BA15" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BB15" s="35" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="BC15" s="25">
         <v>36526</v>
@@ -5704,7 +5726,7 @@
         <v>139</v>
       </c>
       <c r="BX15" s="47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BY15" s="24" t="s">
         <v>141</v>
@@ -5749,7 +5771,7 @@
         <v>98</v>
       </c>
       <c r="CM15" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CN15" s="24" t="s">
         <v>150</v>

--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="171">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -304,10 +304,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699034</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>Failed</t>
   </si>
   <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
@@ -316,10 +313,10 @@
     <t>Hungary</t>
   </si>
   <si>
-    <t>Buck</t>
-  </si>
-  <si>
-    <t>Leffler</t>
+    <t>Gilberto</t>
+  </si>
+  <si>
+    <t>Jacobson</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -407,7 +404,7 @@
     <t>Social Security</t>
   </si>
   <si>
-    <t>666661146</t>
+    <t>666661155</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -473,25 +470,22 @@
     <t>MaidenMothers</t>
   </si>
   <si>
-    <t>Test_3</t>
-  </si>
-  <si>
-    <t>10699033</t>
+    <t>Test_2</t>
   </si>
   <si>
     <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
   <si>
-    <t>Roxanne</t>
-  </si>
-  <si>
-    <t>Wilderman</t>
+    <t>Casey</t>
+  </si>
+  <si>
+    <t>Kuvalis</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Auto 52454838</t>
+    <t>Auto 8625263</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -515,7 +509,7 @@
     <t>Social Security (TAJ) Number</t>
   </si>
   <si>
-    <t>666661145</t>
+    <t>666661154</t>
   </si>
   <si>
     <t>Female</t>
@@ -619,7 +613,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1119,6 +1113,7 @@
     <col min="47" max="47" width="68.54296875" customWidth="1"/>
     <col min="49" max="49" width="24.26953125" customWidth="1"/>
     <col min="50" max="50" width="33.6328125" customWidth="1"/>
+    <col min="51" max="51" width="29.54296875" customWidth="1"/>
     <col min="52" max="52" width="38.453125" customWidth="1"/>
     <col min="53" max="53" width="34.08984375" customWidth="1"/>
     <col min="54" max="54" width="43.26953125" customWidth="1"/>
@@ -1135,6 +1130,7 @@
     <col min="68" max="68" width="45.26953125" customWidth="1"/>
     <col min="69" max="69" width="45.6328125" customWidth="1"/>
     <col min="70" max="70" width="42.36328125" customWidth="1"/>
+    <col min="72" max="72" width="34.453125" customWidth="1"/>
     <col min="78" max="78" width="21.6328125" customWidth="1"/>
     <col min="79" max="79" width="23.26953125" customWidth="1"/>
     <col min="89" max="89" width="29.36328125" customWidth="1"/>
@@ -1453,94 +1449,92 @@
       <c r="A2" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="J2" s="18" t="s">
         <v>103</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>104</v>
       </c>
       <c r="K2" s="19">
         <f t="shared" ref="K2:K3" si="0">TODAY()-31</f>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M2" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="O2" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="Q2" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="R2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="S2" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="T2" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="T2" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="V2" s="25" t="s">
+      <c r="W2" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="W2" s="26" t="s">
-        <v>113</v>
-      </c>
       <c r="X2" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y3" si="1">K2</f>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="Z2" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA2" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="28" t="s">
+      <c r="AC2" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="AC2" s="29" t="s">
+      <c r="AD2" s="30" t="s">
         <v>117</v>
-      </c>
-      <c r="AD2" s="30" t="s">
-        <v>118</v>
       </c>
       <c r="AE2" s="20">
         <v>846</v>
@@ -1552,88 +1546,88 @@
         <v>40</v>
       </c>
       <c r="AH2" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI2" s="20" t="s">
         <v>119</v>
-      </c>
-      <c r="AI2" s="20" t="s">
-        <v>120</v>
       </c>
       <c r="AJ2" s="31">
         <f>TODAY()+365</f>
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="AK2" s="31">
         <f t="shared" ref="AK2:AK3" si="2">Y2+90</f>
-        <v>45845</v>
+        <v>45851</v>
       </c>
       <c r="AL2" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM2" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="AM2" s="30" t="s">
+      <c r="AN2" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="AN2" s="29" t="s">
+      <c r="AO2" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="AO2" s="18" t="s">
+      <c r="AP2" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="AP2" s="32" t="s">
+      <c r="AQ2" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AR2" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS2" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT2" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="AR2" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AS2" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT2" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="AU2" s="33" t="str">
         <f>AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AW2" s="34">
         <f t="shared" ref="AW2:AW3" si="3">Y2-1</f>
-        <v>45754</v>
+        <v>45760</v>
       </c>
       <c r="AX2" s="34">
         <f t="shared" ref="AX2:AX3" si="4">Y2-1</f>
-        <v>45754</v>
+        <v>45760</v>
       </c>
       <c r="AY2" s="35">
         <f t="shared" ref="AY2:AY3" si="5">AJ2</f>
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="AZ2" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BA2" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB2" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="BB2" s="36" t="s">
+      <c r="BC2" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="BC2" s="25" t="s">
+      <c r="BD2" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="BD2" s="25" t="s">
+      <c r="BE2" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF2" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="BE2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF2" s="24" t="s">
-        <v>133</v>
-      </c>
       <c r="BG2" s="37">
-        <v>5555005047</v>
+        <v>5555005054</v>
       </c>
       <c r="BH2" s="25">
         <v>36526</v>
@@ -1642,118 +1636,118 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="BK2" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="BK2" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="BL2" s="38">
         <v>32875</v>
       </c>
       <c r="BM2" s="39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BN2" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BO2" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP2" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="BQ2" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="BP2" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="BQ2" s="24" t="s">
+      <c r="BR2" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BS2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT2" s="30">
+        <v>10</v>
+      </c>
+      <c r="BU2" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="BR2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BS2" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="BT2" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU2" s="40" t="s">
+      <c r="BV2" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="BV2" s="40" t="s">
+      <c r="BW2" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="BW2" s="24" t="s">
+      <c r="BX2" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="BX2" s="18" t="s">
+      <c r="BY2" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="BY2" s="24" t="s">
+      <c r="BZ2" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="BZ2" s="24" t="s">
+      <c r="CA2" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="CA2" s="24" t="s">
+      <c r="CB2" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="CB2" s="24" t="s">
+      <c r="CC2" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="CD2" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="CE2" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="CF2" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="CC2" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="CD2" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="CE2" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="CF2" s="24" t="s">
+      <c r="CG2" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="CG2" s="24" t="s">
-        <v>147</v>
-      </c>
       <c r="CH2" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="CI2" s="42">
         <v>100</v>
       </c>
       <c r="CJ2" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="CK2" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="CK2" s="24" t="s">
+      <c r="CL2" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="CM2" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="CL2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="CM2" s="24" t="s">
+      <c r="CN2" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="CN2" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="CO2" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CP2" s="43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CQ2" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CR2" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CS2" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CU2" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="CV2">
         <v>40</v>
@@ -1761,53 +1755,51 @@
     </row>
     <row r="3" ht="72.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="E3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="G3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>156</v>
-      </c>
       <c r="H3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="J3" s="18" t="s">
         <v>103</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>104</v>
       </c>
       <c r="K3" s="19">
         <f t="shared" si="0"/>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O3" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" s="45" t="s">
         <v>107</v>
-      </c>
-      <c r="P3" s="45" t="s">
-        <v>108</v>
       </c>
       <c r="Q3" s="18">
         <v>123</v>
@@ -1816,41 +1808,41 @@
         <v>1046</v>
       </c>
       <c r="S3" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="T3" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="V3" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="V3" s="25" t="s">
+      <c r="W3" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="W3" s="26" t="s">
-        <v>113</v>
-      </c>
       <c r="X3" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="1"/>
-        <v>45755</v>
+        <v>45761</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA3" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB3" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC3" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AD3" s="30" t="s">
         <v>159</v>
-      </c>
-      <c r="AC3" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AD3" s="30" t="s">
-        <v>161</v>
       </c>
       <c r="AE3" s="20">
         <v>846</v>
@@ -1862,72 +1854,72 @@
         <v>10</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AI3" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AJ3" s="46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AK3" s="31">
         <f t="shared" si="2"/>
-        <v>45845</v>
+        <v>45851</v>
       </c>
       <c r="AL3" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AM3" s="29" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AO3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP3" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="AP3" s="29" t="s">
+      <c r="AQ3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="AQ3" s="18" t="s">
+      <c r="AR3" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS3" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT3" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="AR3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AS3" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT3" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="AU3" s="32" t="str">
         <f t="shared" ref="AU3" si="6">AB3</f>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AW3" s="34">
         <f t="shared" si="3"/>
-        <v>45754</v>
+        <v>45760</v>
       </c>
       <c r="AX3" s="34">
         <f t="shared" si="4"/>
-        <v>45754</v>
+        <v>45760</v>
       </c>
       <c r="AY3" s="47" t="str">
         <f t="shared" si="5"/>
         <v>N/A</v>
       </c>
       <c r="AZ3" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="BB3" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BC3" s="25">
         <v>36526</v>
@@ -1936,13 +1928,13 @@
         <v>51136</v>
       </c>
       <c r="BE3" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BF3" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BG3" s="37">
-        <v>5555005046</v>
+        <v>5555005054</v>
       </c>
       <c r="BH3" s="25">
         <v>36526</v>
@@ -1951,112 +1943,112 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BL3" s="38">
         <v>32875</v>
       </c>
       <c r="BM3" s="39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BN3" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BO3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP3" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="BQ3" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="BP3" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="BQ3" s="24" t="s">
+      <c r="BR3" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BS3" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BT3" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BU3" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="BR3" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BS3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="BT3" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU3" s="40" t="s">
+      <c r="BV3" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="BV3" s="40" t="s">
+      <c r="BW3" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="BW3" s="24" t="s">
+      <c r="BX3" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="BY3" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="BZ3" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="CA3" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB3" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="CC3" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="CD3" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="BX3" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="BY3" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="BZ3" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="CA3" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="CB3" s="24" t="s">
+      <c r="CE3" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="CF3" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="CC3" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="CE3" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="CF3" s="24" t="s">
+      <c r="CG3" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="CG3" s="24" t="s">
-        <v>147</v>
-      </c>
       <c r="CH3" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="CI3" s="42">
         <v>100</v>
       </c>
       <c r="CJ3" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="CK3" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="CK3" s="24" t="s">
-        <v>149</v>
-      </c>
       <c r="CL3" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="CM3" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="CN3" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="CO3" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="CP3" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="CN3" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="CO3" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="CP3" s="30" t="s">
-        <v>171</v>
-      </c>
       <c r="CQ3" s="43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="CR3" s="49">
         <v>31048</v>
       </c>
       <c r="CS3" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="CT3" s="42">
         <v>1234011</v>

--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CFF3B6-9AB3-4953-99BB-D57856603B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -318,13 +304,10 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Ivah Armstrong' Employee:{10699066}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('button:has-text("Done")')[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10699219</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
@@ -333,10 +316,10 @@
     <t>Hungary</t>
   </si>
   <si>
-    <t>Ivah</t>
-  </si>
-  <si>
-    <t>Armstrong</t>
+    <t>Francisca</t>
+  </si>
+  <si>
+    <t>Haley</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -399,7 +382,7 @@
     <t>Automation Comments here….</t>
   </si>
   <si>
-    <t>94 Retail Operatives </t>
+    <t xml:space="preserve">94 Retail Operatives </t>
   </si>
   <si>
     <t>16 Men’s Accessories</t>
@@ -424,7 +407,7 @@
     <t>Social Security</t>
   </si>
   <si>
-    <t>666661150</t>
+    <t>666661172</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -490,22 +473,25 @@
     <t>MaidenMothers</t>
   </si>
   <si>
-    <t>Test_2</t>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t>10699220</t>
   </si>
   <si>
     <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
   <si>
-    <t>Casey</t>
-  </si>
-  <si>
-    <t>Kuvalis</t>
+    <t>Nya</t>
+  </si>
+  <si>
+    <t>Wiza</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Auto 8625263</t>
+    <t>Auto 65281508</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -520,7 +506,7 @@
     <t>IRREGULAR - Irregular Shift Pattern (Hungary Regular &amp; Irregular Shift Pattern-Hungary)</t>
   </si>
   <si>
-    <t>92 Retail Management </t>
+    <t xml:space="preserve">92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -529,7 +515,7 @@
     <t>Social Security (TAJ) Number</t>
   </si>
   <si>
-    <t>666661151</t>
+    <t>666661173</t>
   </si>
   <si>
     <t>Female</t>
@@ -553,57 +539,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -615,13 +601,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,7 +619,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -647,91 +633,51 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1146,9 +1092,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CV4"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="57.6328125" customWidth="1"/>
@@ -1201,7 +1147,7 @@
     <col min="100" max="100" width="20.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1449,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:100" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="87.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -1535,8 +1481,8 @@
         <v>104</v>
       </c>
       <c r="K2" s="19">
-        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <f t="shared" ref="K2:K3" si="0">TODAY()-31</f>
+        <v>45766</v>
       </c>
       <c r="L2" s="20" t="s">
         <v>99</v>
@@ -1578,8 +1524,8 @@
         <v>104</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" ca="1" si="1">K2</f>
-        <v>45761</v>
+        <f t="shared" ref="Y2:Y3" si="1">K2</f>
+        <v>45766</v>
       </c>
       <c r="Z2" s="18" t="s">
         <v>114</v>
@@ -1612,12 +1558,12 @@
         <v>120</v>
       </c>
       <c r="AJ2" s="31">
-        <f ca="1">TODAY()+365</f>
-        <v>46157</v>
+        <f>TODAY()+365</f>
+        <v>46162</v>
       </c>
       <c r="AK2" s="31">
-        <f t="shared" ref="AK2:AK3" ca="1" si="2">Y2+90</f>
-        <v>45851</v>
+        <f t="shared" ref="AK2:AK3" si="2">Y2+90</f>
+        <v>45856</v>
       </c>
       <c r="AL2" s="18" t="s">
         <v>121</v>
@@ -1654,16 +1600,16 @@
         <v>128</v>
       </c>
       <c r="AW2" s="34">
-        <f t="shared" ref="AW2:AW3" ca="1" si="3">Y2-1</f>
-        <v>45760</v>
+        <f t="shared" ref="AW2:AW3" si="3">Y2-1</f>
+        <v>45765</v>
       </c>
       <c r="AX2" s="34">
-        <f t="shared" ref="AX2:AX3" ca="1" si="4">Y2-1</f>
-        <v>45760</v>
+        <f t="shared" ref="AX2:AX3" si="4">Y2-1</f>
+        <v>45765</v>
       </c>
       <c r="AY2" s="35">
-        <f t="shared" ref="AY2:AY3" ca="1" si="5">AJ2</f>
-        <v>46157</v>
+        <f t="shared" ref="AY2:AY3" si="5">AJ2</f>
+        <v>46162</v>
       </c>
       <c r="AZ2" s="24" t="s">
         <v>99</v>
@@ -1687,7 +1633,7 @@
         <v>133</v>
       </c>
       <c r="BG2" s="37">
-        <v>5555005050</v>
+        <v>5555005100</v>
       </c>
       <c r="BH2" s="25">
         <v>36526</v>
@@ -1813,25 +1759,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:100" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="72.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="44"/>
+      <c r="B3" s="44" t="s">
+        <v>153</v>
+      </c>
       <c r="C3" s="13" t="s">
         <v>97</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>99</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>102</v>
@@ -1843,8 +1791,8 @@
         <v>104</v>
       </c>
       <c r="K3" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>45761</v>
+        <f t="shared" si="0"/>
+        <v>45766</v>
       </c>
       <c r="L3" s="20" t="s">
         <v>99</v>
@@ -1853,7 +1801,7 @@
         <v>105</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O3" s="22" t="s">
         <v>107</v>
@@ -1886,23 +1834,23 @@
         <v>104</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" ca="1" si="1"/>
-        <v>45761</v>
+        <f t="shared" si="1"/>
+        <v>45766</v>
       </c>
       <c r="Z3" s="18" t="s">
         <v>114</v>
       </c>
       <c r="AA3" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AB3" s="32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC3" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD3" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AE3" s="20">
         <v>846</v>
@@ -1914,7 +1862,7 @@
         <v>10</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AI3" s="20" t="s">
         <v>120</v>
@@ -1923,17 +1871,17 @@
         <v>115</v>
       </c>
       <c r="AK3" s="31">
-        <f t="shared" ca="1" si="2"/>
-        <v>45851</v>
+        <f t="shared" si="2"/>
+        <v>45856</v>
       </c>
       <c r="AL3" s="18" t="s">
         <v>121</v>
       </c>
       <c r="AM3" s="29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO3" s="18" t="s">
         <v>124</v>
@@ -1961,12 +1909,12 @@
         <v>128</v>
       </c>
       <c r="AW3" s="34">
-        <f t="shared" ca="1" si="3"/>
-        <v>45760</v>
+        <f t="shared" si="3"/>
+        <v>45765</v>
       </c>
       <c r="AX3" s="34">
-        <f t="shared" ca="1" si="4"/>
-        <v>45760</v>
+        <f t="shared" si="4"/>
+        <v>45765</v>
       </c>
       <c r="AY3" s="47" t="str">
         <f t="shared" si="5"/>
@@ -1976,10 +1924,10 @@
         <v>99</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BB3" s="36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BC3" s="25">
         <v>36526</v>
@@ -1994,7 +1942,7 @@
         <v>133</v>
       </c>
       <c r="BG3" s="37">
-        <v>5555005051</v>
+        <v>5555005101</v>
       </c>
       <c r="BH3" s="25">
         <v>36526</v>
@@ -2006,7 +1954,7 @@
         <v>134</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BL3" s="38">
         <v>32875</v>
@@ -2045,7 +1993,7 @@
         <v>140</v>
       </c>
       <c r="BX3" s="48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BY3" s="24" t="s">
         <v>142</v>
@@ -2090,16 +2038,16 @@
         <v>99</v>
       </c>
       <c r="CM3" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CN3" s="24" t="s">
         <v>151</v>
       </c>
       <c r="CO3" s="32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CP3" s="30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CQ3" s="43" t="s">
         <v>111</v>
@@ -2108,7 +2056,7 @@
         <v>31048</v>
       </c>
       <c r="CS3" s="30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CT3" s="42">
         <v>1234011</v>
@@ -2120,23 +2068,56 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="14.5" customHeight="1" spans="36:36" x14ac:dyDescent="0.25">
       <c r="AJ4" s="50"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 Z2 X2 U2 I2:J2 CC2:CC3 BW2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3 Z3 X3 U3 I3:J3 BW3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2:CC3">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="W3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="W2" r:id="rId1"/>
+    <hyperlink ref="W3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/testDataHungry.xlsx
+++ b/Data/testDataHungry.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBF2F9F-19D3-4C1F-9F6A-BE62D0E7FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="170">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -304,12 +318,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699219</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
   </si>
   <si>
@@ -382,7 +390,7 @@
     <t>Automation Comments here….</t>
   </si>
   <si>
-    <t xml:space="preserve">94 Retail Operatives </t>
+    <t>94 Retail Operatives </t>
   </si>
   <si>
     <t>16 Men’s Accessories</t>
@@ -407,9 +415,6 @@
     <t>Social Security</t>
   </si>
   <si>
-    <t>666661172</t>
-  </si>
-  <si>
     <t>01/01/2000</t>
   </si>
   <si>
@@ -476,9 +481,6 @@
     <t>Test_3</t>
   </si>
   <si>
-    <t>10699220</t>
-  </si>
-  <si>
     <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
   <si>
@@ -491,7 +493,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>Auto 65281508</t>
+    <t>Auto 92607314</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -506,7 +508,7 @@
     <t>IRREGULAR - Irregular Shift Pattern (Hungary Regular &amp; Irregular Shift Pattern-Hungary)</t>
   </si>
   <si>
-    <t xml:space="preserve">92 Retail Management </t>
+    <t>92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -515,9 +517,6 @@
     <t>Social Security (TAJ) Number</t>
   </si>
   <si>
-    <t>666661173</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
@@ -534,62 +533,68 @@
   </si>
   <si>
     <t>Mammy</t>
+  </si>
+  <si>
+    <t>666661208</t>
+  </si>
+  <si>
+    <t>666661209</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -601,13 +606,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,7 +624,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -633,51 +638,91 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1092,9 +1137,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CV4"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="57.6328125" customWidth="1"/>
@@ -1147,7 +1192,7 @@
     <col min="100" max="100" width="20.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:100" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,98 +1494,94 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" ht="87.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:100" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="K2" s="19">
+        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-31</f>
+        <v>45774</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="M2" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="N2" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="K2" s="19">
-        <f t="shared" ref="K2:K3" si="0">TODAY()-31</f>
-        <v>45766</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="M2" s="21" t="s">
+      <c r="O2" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="P2" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="Q2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="R2" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="S2" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="T2" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="W2" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="T2" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="V2" s="25" t="s">
+      <c r="X2" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y2" s="19">
+        <f t="shared" ref="Y2:Y3" ca="1" si="1">K2</f>
+        <v>45774</v>
+      </c>
+      <c r="Z2" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="AA2" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="X2" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" si="1">K2</f>
-        <v>45766</v>
-      </c>
-      <c r="Z2" s="18" t="s">
+      <c r="AB2" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AC2" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="28" t="s">
+      <c r="AD2" s="30" t="s">
         <v>116</v>
-      </c>
-      <c r="AC2" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" s="30" t="s">
-        <v>118</v>
       </c>
       <c r="AE2" s="20">
         <v>846</v>
@@ -1552,88 +1593,88 @@
         <v>40</v>
       </c>
       <c r="AH2" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI2" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ2" s="31">
+        <f ca="1">TODAY()+365</f>
+        <v>46170</v>
+      </c>
+      <c r="AK2" s="31">
+        <f t="shared" ref="AK2:AK3" ca="1" si="2">Y2+90</f>
+        <v>45864</v>
+      </c>
+      <c r="AL2" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AM2" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="AJ2" s="31">
-        <f>TODAY()+365</f>
-        <v>46162</v>
-      </c>
-      <c r="AK2" s="31">
-        <f t="shared" ref="AK2:AK3" si="2">Y2+90</f>
-        <v>45856</v>
-      </c>
-      <c r="AL2" s="18" t="s">
+      <c r="AN2" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="AM2" s="30" t="s">
+      <c r="AO2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="AN2" s="29" t="s">
+      <c r="AP2" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="AO2" s="18" t="s">
+      <c r="AQ2" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="AP2" s="32" t="s">
+      <c r="AR2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS2" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT2" s="18" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ2" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="AR2" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AS2" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT2" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="AU2" s="33" t="str">
         <f>AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW2" s="34">
+        <f t="shared" ref="AW2:AW3" ca="1" si="3">Y2-1</f>
+        <v>45773</v>
+      </c>
+      <c r="AX2" s="34">
+        <f t="shared" ref="AX2:AX3" ca="1" si="4">Y2-1</f>
+        <v>45773</v>
+      </c>
+      <c r="AY2" s="35">
+        <f t="shared" ref="AY2:AY3" ca="1" si="5">AJ2</f>
+        <v>46170</v>
+      </c>
+      <c r="AZ2" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB2" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="BC2" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="AW2" s="34">
-        <f t="shared" ref="AW2:AW3" si="3">Y2-1</f>
-        <v>45765</v>
-      </c>
-      <c r="AX2" s="34">
-        <f t="shared" ref="AX2:AX3" si="4">Y2-1</f>
-        <v>45765</v>
-      </c>
-      <c r="AY2" s="35">
-        <f t="shared" ref="AY2:AY3" si="5">AJ2</f>
-        <v>46162</v>
-      </c>
-      <c r="AZ2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BA2" s="24" t="s">
+      <c r="BD2" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="BB2" s="36" t="s">
+      <c r="BE2" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="BF2" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="BC2" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="BD2" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF2" s="24" t="s">
-        <v>133</v>
-      </c>
       <c r="BG2" s="37">
-        <v>5555005100</v>
+        <v>5555005301</v>
       </c>
       <c r="BH2" s="25">
         <v>36526</v>
@@ -1642,172 +1683,168 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BK2" s="29" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BL2" s="38">
         <v>32875</v>
       </c>
       <c r="BM2" s="39" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BN2" s="24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO2" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="BP2" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="BR2" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="BS2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT2" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU2" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="BV2" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="BP2" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="BQ2" s="24" t="s">
+      <c r="BW2" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="BR2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BS2" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="BT2" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU2" s="40" t="s">
+      <c r="BX2" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BV2" s="40" t="s">
+      <c r="BY2" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="BW2" s="24" t="s">
+      <c r="BZ2" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="BX2" s="18" t="s">
+      <c r="CA2" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="BY2" s="24" t="s">
+      <c r="CB2" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="BZ2" s="24" t="s">
+      <c r="CC2" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="CD2" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="CE2" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="CF2" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="CA2" s="24" t="s">
+      <c r="CG2" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="CB2" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="CC2" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="CD2" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="CE2" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="CF2" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="CG2" s="24" t="s">
-        <v>147</v>
-      </c>
       <c r="CH2" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="CI2" s="42">
         <v>100</v>
       </c>
       <c r="CJ2" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="CK2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="CL2" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="CM2" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="CN2" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="CK2" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="CL2" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="CM2" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="CN2" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="CO2" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CP2" s="43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CQ2" s="38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CR2" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CS2" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CU2" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="CV2">
         <v>40</v>
       </c>
     </row>
-    <row r="3" ht="72.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:100" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="H3" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="19">
+        <f t="shared" ca="1" si="0"/>
+        <v>45774</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="19">
-        <f t="shared" si="0"/>
-        <v>45766</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="M3" s="21" t="s">
+      <c r="O3" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="O3" s="22" t="s">
-        <v>107</v>
-      </c>
       <c r="P3" s="45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Q3" s="18">
         <v>123</v>
@@ -1816,41 +1853,41 @@
         <v>1046</v>
       </c>
       <c r="S3" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="T3" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="V3" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="V3" s="25" t="s">
+      <c r="X3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y3" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>45774</v>
+      </c>
+      <c r="Z3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="W3" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="X3" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y3" s="19">
-        <f t="shared" si="1"/>
-        <v>45766</v>
-      </c>
-      <c r="Z3" s="18" t="s">
-        <v>114</v>
-      </c>
       <c r="AA3" s="27" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AB3" s="32" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AC3" s="29" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AD3" s="30" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AE3" s="20">
         <v>846</v>
@@ -1862,72 +1899,72 @@
         <v>10</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AI3" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AJ3" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK3" s="31">
-        <f t="shared" si="2"/>
-        <v>45856</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45864</v>
       </c>
       <c r="AL3" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AM3" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AO3" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP3" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="AP3" s="29" t="s">
+      <c r="AR3" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS3" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT3" s="18" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="AR3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AS3" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT3" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="AU3" s="32" t="str">
         <f t="shared" ref="AU3" si="6">AB3</f>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AW3" s="34">
-        <f t="shared" si="3"/>
-        <v>45765</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45773</v>
       </c>
       <c r="AX3" s="34">
-        <f t="shared" si="4"/>
-        <v>45765</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45773</v>
       </c>
       <c r="AY3" s="47" t="str">
         <f t="shared" si="5"/>
         <v>N/A</v>
       </c>
       <c r="AZ3" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="BB3" s="36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="BC3" s="25">
         <v>36526</v>
@@ -1936,13 +1973,13 @@
         <v>51136</v>
       </c>
       <c r="BE3" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BF3" s="24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BG3" s="37">
-        <v>5555005101</v>
+        <v>5555005302</v>
       </c>
       <c r="BH3" s="25">
         <v>36526</v>
@@ -1951,112 +1988,112 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="BL3" s="38">
         <v>32875</v>
       </c>
       <c r="BM3" s="39" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BN3" s="24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="BP3" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ3" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="BR3" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="BS3" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="BV3" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="BP3" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="BQ3" s="24" t="s">
+      <c r="BW3" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="BR3" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="BS3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="BT3" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU3" s="40" t="s">
+      <c r="BX3" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="BY3" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="BZ3" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="CA3" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="CB3" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="CC3" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="CD3" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BV3" s="40" t="s">
+      <c r="CE3" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="BW3" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="BX3" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="BY3" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="BZ3" s="24" t="s">
+      <c r="CF3" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="CA3" s="24" t="s">
+      <c r="CG3" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="CB3" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="CC3" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="CE3" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="CF3" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="CG3" s="24" t="s">
-        <v>147</v>
-      </c>
       <c r="CH3" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="CI3" s="42">
         <v>100</v>
       </c>
       <c r="CJ3" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="CK3" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="CL3" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="CM3" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="CN3" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="CK3" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="CL3" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="CM3" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="CN3" s="24" t="s">
-        <v>151</v>
-      </c>
       <c r="CO3" s="32" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="CP3" s="30" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="CQ3" s="43" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="CR3" s="49">
         <v>31048</v>
       </c>
       <c r="CS3" s="30" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="CT3" s="42">
         <v>1234011</v>
@@ -2068,56 +2105,23 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1" spans="36:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AJ4" s="50"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 Z2 X2 U2 I2:J2 CC2:CC3 BW2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2:CC3">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3 Z3 X3 U3 I3:J3 BW3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="W2" r:id="rId1"/>
-    <hyperlink ref="W3" r:id="rId2"/>
+    <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="W3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>